--- a/src/test/resources/ImportTemplate/Recon.xlsx
+++ b/src/test/resources/ImportTemplate/Recon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2B12B4-AF5A-4EFE-A2A1-195F18033A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9D1171-79E9-4561-9A94-9977CC6A13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Recon--ImportSQL-DB--customer--</t>
+    <t>Recon_ImportSQL-DB-PostgreSQL--Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon.xlsx
+++ b/src/test/resources/ImportTemplate/Recon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9D1171-79E9-4561-9A94-9977CC6A13D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA16306B-BB53-48A2-831A-FFDD735EEC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Recon_ImportSQL-DB-PostgreSQL--Customer</t>
+    <t>RECON_ImportSQL DB PostgreSQL Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon.xlsx
+++ b/src/test/resources/ImportTemplate/Recon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA16306B-BB53-48A2-831A-FFDD735EEC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8631C8-40FF-4619-BADE-08D273985702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>RECON_ImportSQL DB PostgreSQL Customer</t>
+    <t>Recon_ImportSQL--DB-PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon.xlsx
+++ b/src/test/resources/ImportTemplate/Recon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8631C8-40FF-4619-BADE-08D273985702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3327F308-6741-49C2-920F-1C19B9439E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>select * from public.customer</t>
   </si>
   <si>
-    <t>Recon_ImportSQL--DB-PostgreSQL_Customer</t>
+    <t>Recon_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon.xlsx
+++ b/src/test/resources/ImportTemplate/Recon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3327F308-6741-49C2-920F-1C19B9439E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490B496E-908E-4C0E-86DD-F6BE8FB0261C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,10 @@
     <t>targetSql</t>
   </si>
   <si>
-    <t>select * from public.customer</t>
+    <t>Recon_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
   <si>
-    <t>Recon_ImportSQL__DB_PostgreSQL_Customer</t>
+    <t>select * from icedq.customer</t>
   </si>
 </sst>
 </file>
@@ -386,13 +386,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
